--- a/reports/Debug-snowbowl-20251216/For The Day (Prior Year)_PayrollHistory.xlsx
+++ b/reports/Debug-snowbowl-20251216/For The Day (Prior Year)_PayrollHistory.xlsx
@@ -25,6 +25,81 @@
     <t>D8030</t>
   </si>
   <si>
+    <t>D1020</t>
+  </si>
+  <si>
+    <t>D1060</t>
+  </si>
+  <si>
+    <t>D1070</t>
+  </si>
+  <si>
+    <t>D9007</t>
+  </si>
+  <si>
+    <t>D1030</t>
+  </si>
+  <si>
+    <t>D3050</t>
+  </si>
+  <si>
+    <t>D4031</t>
+  </si>
+  <si>
+    <t>D5110</t>
+  </si>
+  <si>
+    <t>D5113</t>
+  </si>
+  <si>
+    <t>D6030</t>
+  </si>
+  <si>
+    <t>D6740</t>
+  </si>
+  <si>
+    <t>D1000</t>
+  </si>
+  <si>
+    <t>D4032</t>
+  </si>
+  <si>
+    <t>D6700</t>
+  </si>
+  <si>
+    <t>D6730</t>
+  </si>
+  <si>
+    <t>D7010</t>
+  </si>
+  <si>
+    <t>D1200</t>
+  </si>
+  <si>
+    <t>D5111</t>
+  </si>
+  <si>
+    <t>D6215</t>
+  </si>
+  <si>
+    <t>D8050</t>
+  </si>
+  <si>
+    <t>D8060</t>
+  </si>
+  <si>
+    <t>D2000</t>
+  </si>
+  <si>
+    <t>D4034</t>
+  </si>
+  <si>
+    <t>D8010</t>
+  </si>
+  <si>
+    <t>D8020</t>
+  </si>
+  <si>
     <t>D1100</t>
   </si>
   <si>
@@ -44,81 +119,6 @@
   </si>
   <si>
     <t>D8040</t>
-  </si>
-  <si>
-    <t>D1000</t>
-  </si>
-  <si>
-    <t>D4032</t>
-  </si>
-  <si>
-    <t>D6700</t>
-  </si>
-  <si>
-    <t>D6730</t>
-  </si>
-  <si>
-    <t>D7010</t>
-  </si>
-  <si>
-    <t>D2000</t>
-  </si>
-  <si>
-    <t>D4034</t>
-  </si>
-  <si>
-    <t>D8010</t>
-  </si>
-  <si>
-    <t>D8020</t>
-  </si>
-  <si>
-    <t>D1200</t>
-  </si>
-  <si>
-    <t>D5111</t>
-  </si>
-  <si>
-    <t>D6215</t>
-  </si>
-  <si>
-    <t>D8050</t>
-  </si>
-  <si>
-    <t>D8060</t>
-  </si>
-  <si>
-    <t>D1020</t>
-  </si>
-  <si>
-    <t>D1060</t>
-  </si>
-  <si>
-    <t>D1070</t>
-  </si>
-  <si>
-    <t>D9007</t>
-  </si>
-  <si>
-    <t>D1030</t>
-  </si>
-  <si>
-    <t>D3050</t>
-  </si>
-  <si>
-    <t>D4031</t>
-  </si>
-  <si>
-    <t>D5110</t>
-  </si>
-  <si>
-    <t>D5113</t>
-  </si>
-  <si>
-    <t>D6030</t>
-  </si>
-  <si>
-    <t>D6740</t>
   </si>
   <si>
     <t>D1010</t>
@@ -521,7 +521,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="2">
-        <v>765.57</v>
+        <v>1136.12</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -529,7 +529,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="2">
-        <v>2273.04</v>
+        <v>409.29</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -537,7 +537,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="2">
-        <v>928.53</v>
+        <v>956.38</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -545,7 +545,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="2">
-        <v>256.29</v>
+        <v>206.58</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -553,7 +553,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="2">
-        <v>404.81</v>
+        <v>1942.14</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -561,7 +561,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="2">
-        <v>125.29</v>
+        <v>313.27</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -569,7 +569,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="2">
-        <v>850.57</v>
+        <v>163.13</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -577,7 +577,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="2">
-        <v>897.27</v>
+        <v>1213.00</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -585,7 +585,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="2">
-        <v>313.18</v>
+        <v>110.82</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -593,7 +593,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="2">
-        <v>208.58</v>
+        <v>627.03</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -601,7 +601,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="2">
-        <v>170.33</v>
+        <v>978.35</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -609,7 +609,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="2">
-        <v>302.20</v>
+        <v>897.27</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -617,7 +617,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="2">
-        <v>3329.72</v>
+        <v>313.18</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -625,7 +625,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="2">
-        <v>142.80</v>
+        <v>208.58</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -633,7 +633,7 @@
         <v>17</v>
       </c>
       <c r="B17" s="2">
-        <v>931.04</v>
+        <v>170.33</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -641,7 +641,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="2">
-        <v>755.42</v>
+        <v>302.20</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -689,7 +689,7 @@
         <v>24</v>
       </c>
       <c r="B24" s="2">
-        <v>1136.12</v>
+        <v>3329.72</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -697,7 +697,7 @@
         <v>25</v>
       </c>
       <c r="B25" s="2">
-        <v>409.29</v>
+        <v>142.80</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -705,7 +705,7 @@
         <v>26</v>
       </c>
       <c r="B26" s="2">
-        <v>956.38</v>
+        <v>931.04</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -713,7 +713,7 @@
         <v>27</v>
       </c>
       <c r="B27" s="2">
-        <v>206.58</v>
+        <v>755.42</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -721,7 +721,7 @@
         <v>28</v>
       </c>
       <c r="B28" s="2">
-        <v>1942.14</v>
+        <v>765.57</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -729,7 +729,7 @@
         <v>29</v>
       </c>
       <c r="B29" s="2">
-        <v>313.27</v>
+        <v>2273.04</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -737,7 +737,7 @@
         <v>30</v>
       </c>
       <c r="B30" s="2">
-        <v>163.13</v>
+        <v>928.53</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -745,7 +745,7 @@
         <v>31</v>
       </c>
       <c r="B31" s="2">
-        <v>1213.00</v>
+        <v>256.29</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -753,7 +753,7 @@
         <v>32</v>
       </c>
       <c r="B32" s="2">
-        <v>110.82</v>
+        <v>404.81</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -761,7 +761,7 @@
         <v>33</v>
       </c>
       <c r="B33" s="2">
-        <v>627.03</v>
+        <v>125.29</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -769,7 +769,7 @@
         <v>34</v>
       </c>
       <c r="B34" s="2">
-        <v>978.35</v>
+        <v>850.57</v>
       </c>
     </row>
     <row r="35" spans="1:2">
